--- a/curiculam_CE.xlsx
+++ b/curiculam_CE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\my_timetable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32BC652C-A70C-4703-8141-50CD75147487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E728F20F-3519-47F8-A9AD-015049490D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1695" yWindow="3300" windowWidth="22560" windowHeight="10305" activeTab="6" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
+    <workbookView xWindow="990" yWindow="5100" windowWidth="17925" windowHeight="10305" activeTab="6" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
   </bookViews>
   <sheets>
     <sheet name="s1" sheetId="1" r:id="rId1"/>
@@ -2950,8 +2950,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="50.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7.7109375" customWidth="1"/>
     <col min="5" max="5" width="5.140625" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
